--- a/Result/profitability/9929.xlsx
+++ b/Result/profitability/9929.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-0.21</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.02250000000000008</v>
+        <v>0.02249999999999992</v>
       </c>
       <c r="N2" t="n">
-        <v>13.47</v>
+        <v>14.83</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.02</v>
       </c>
       <c r="M3" t="n">
-        <v>0.002499999999999917</v>
+        <v>0.01874999999999992</v>
       </c>
       <c r="N3" t="n">
-        <v>13.1175</v>
+        <v>14.24375</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.09</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.01500000000000008</v>
+        <v>0.02124999999999992</v>
       </c>
       <c r="N4" t="n">
-        <v>12.43625</v>
+        <v>13.9375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.36</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.04625000000000008</v>
+        <v>-0.01875000000000008</v>
       </c>
       <c r="N5" t="n">
-        <v>11.7225</v>
+        <v>13.08</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.05000000000000009</v>
+        <v>-0.02250000000000008</v>
       </c>
       <c r="N6" t="n">
-        <v>11.055</v>
+        <v>11.80125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.03625000000000008</v>
+        <v>-0.03000000000000008</v>
       </c>
       <c r="N7" t="n">
-        <v>10.27375</v>
+        <v>10.3875</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>-0.05</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.05875000000000008</v>
+        <v>-0.06375000000000008</v>
       </c>
       <c r="N8" t="n">
-        <v>8.578750000000001</v>
+        <v>8.1875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1518,7 +1518,7 @@
         <v>0.05</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.08000000000000007</v>
+        <v>-0.08000000000000008</v>
       </c>
       <c r="N9" t="n">
         <v>6.265000000000001</v>
@@ -9804,6 +9804,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>9929</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>164</v>
+      </c>
+      <c r="D75" t="n">
+        <v>128</v>
+      </c>
+      <c r="E75" t="n">
+        <v>35</v>
+      </c>
+      <c r="F75" t="n">
+        <v>21.65</v>
+      </c>
+      <c r="G75" t="n">
+        <v>15</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>9.00%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>4</v>
+      </c>
+      <c r="J75" t="n">
+        <v>19</v>
+      </c>
+      <c r="K75" t="n">
+        <v>18</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.02624999999999992</v>
+      </c>
+      <c r="N75" t="n">
+        <v>15.83625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.04000000000000001</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.1818181818181819</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-3.130000000000003</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.126311541565779</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.006487488415199</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
